--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AppointmentQuestionnaireResponse</t>
+    <t>PreadmissionAppointmentQuestionnaireResponseFr</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T09:05:02+00:00</t>
+    <t>2025-04-24T12:12:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:53:37+00:00</t>
+    <t>2025-04-25T09:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-questionnaire-response</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-questionnaire-response</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T14:29:23+00:00</t>
+    <t>2025-04-25T16:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/appointment-questionnaire-response</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/appointment-questionnaire-response</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T10:41:02+00:00</t>
+    <t>2025-05-05T08:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T13:54:59+00:00</t>
+    <t>2025-05-14T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Questionnaire lié au rendez-vous</t>
+    <t>Fr QuestionnaireResponse de préadmission</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:00:47+00:00</t>
+    <t>2025-05-22T16:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
+++ b/nmoreau/ig/StructureDefinition-appointment-questionnaire-response.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
